--- a/数据质量预评估表.xlsx
+++ b/数据质量预评估表.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>❌ ods_order 600 组重复，其余 5 表主键唯一</t>
+          <t>❌ ods_order 600 条冗余重复（586 组），其余 5 表主键唯一</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>每组各出现 2 次（如 O2024000008、O2024000009…）</t>
+          <t>600 条冗余（586 组）：573 组×2、12 组×3、1 组×4（如 O2024000008、O2024000009…）</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>15600 → 15000，removed_cnt=600，与重复组数完全吻合；distinct=15000=total_rows</t>
+          <t>15600 → 15000，removed_cnt=600（=冗余行数），与唯一性评估口径吻合；distinct=15000=total_rows</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
